--- a/public/plantilla-anticipo.xlsx
+++ b/public/plantilla-anticipo.xlsx
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,11 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -287,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -307,46 +312,46 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -394,17 +399,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -417,7 +422,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -432,13 +437,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -468,10 +473,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,11 +494,55 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,9 +1048,9 @@
       </c>
       <c r="B10" s="76" t="n"/>
       <c r="C10" s="77" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="76" t="n"/>
-      <c r="F10" s="77" t="n"/>
+      <c r="D10" s="84" t="n"/>
+      <c r="E10" s="85" t="n"/>
+      <c r="F10" s="86" t="n"/>
       <c r="G10" s="21" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1009,9 +1058,9 @@
       </c>
       <c r="H10" s="76" t="n"/>
       <c r="I10" s="77" t="n"/>
-      <c r="J10" s="23" t="n"/>
-      <c r="K10" s="76" t="n"/>
-      <c r="L10" s="77" t="n"/>
+      <c r="J10" s="84" t="n"/>
+      <c r="K10" s="85" t="n"/>
+      <c r="L10" s="86" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="33">
       <c r="A11" s="21" t="inlineStr">
@@ -1021,9 +1070,9 @@
       </c>
       <c r="B11" s="76" t="n"/>
       <c r="C11" s="77" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="76" t="n"/>
-      <c r="F11" s="77" t="n"/>
+      <c r="D11" s="84" t="n"/>
+      <c r="E11" s="85" t="n"/>
+      <c r="F11" s="86" t="n"/>
       <c r="G11" s="21" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1031,9 +1080,9 @@
       </c>
       <c r="H11" s="76" t="n"/>
       <c r="I11" s="77" t="n"/>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="76" t="n"/>
-      <c r="L11" s="77" t="n"/>
+      <c r="J11" s="84" t="n"/>
+      <c r="K11" s="85" t="n"/>
+      <c r="L11" s="86" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="33">
       <c r="A12" s="21" t="inlineStr">
@@ -1043,9 +1092,9 @@
       </c>
       <c r="B12" s="76" t="n"/>
       <c r="C12" s="77" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="76" t="n"/>
-      <c r="F12" s="77" t="n"/>
+      <c r="D12" s="84" t="n"/>
+      <c r="E12" s="85" t="n"/>
+      <c r="F12" s="86" t="n"/>
       <c r="G12" s="21" t="inlineStr">
         <is>
           <t>Fecha del anticipo</t>
@@ -1053,9 +1102,9 @@
       </c>
       <c r="H12" s="76" t="n"/>
       <c r="I12" s="77" t="n"/>
-      <c r="J12" s="23" t="n"/>
-      <c r="K12" s="76" t="n"/>
-      <c r="L12" s="77" t="n"/>
+      <c r="J12" s="84" t="n"/>
+      <c r="K12" s="85" t="n"/>
+      <c r="L12" s="86" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="33">
       <c r="A13" s="39" t="inlineStr">
@@ -1083,7 +1132,7 @@
       </c>
       <c r="B14" s="76" t="n"/>
       <c r="C14" s="77" t="n"/>
-      <c r="D14" s="82" t="n"/>
+      <c r="D14" s="87" t="n"/>
       <c r="E14" s="76" t="n"/>
       <c r="F14" s="77" t="n"/>
       <c r="G14" s="80" t="inlineStr">
@@ -1105,7 +1154,7 @@
       </c>
       <c r="B15" s="76" t="n"/>
       <c r="C15" s="77" t="n"/>
-      <c r="D15" s="83" t="n"/>
+      <c r="D15" s="88" t="n"/>
       <c r="E15" s="76" t="n"/>
       <c r="F15" s="77" t="n"/>
       <c r="G15" s="48" t="n"/>
@@ -1119,7 +1168,7 @@
       </c>
       <c r="B16" s="76" t="n"/>
       <c r="C16" s="77" t="n"/>
-      <c r="D16" s="81">
+      <c r="D16" s="89">
         <f>IF(OR(D14="",D15=""),"",D14*D15)</f>
         <v/>
       </c>
@@ -1136,7 +1185,7 @@
       </c>
       <c r="B17" s="76" t="n"/>
       <c r="C17" s="77" t="n"/>
-      <c r="D17" s="83" t="n"/>
+      <c r="D17" s="88" t="n"/>
       <c r="E17" s="76" t="n"/>
       <c r="F17" s="77" t="n"/>
       <c r="G17" s="48" t="n"/>
@@ -1150,7 +1199,7 @@
       </c>
       <c r="B18" s="76" t="n"/>
       <c r="C18" s="77" t="n"/>
-      <c r="D18" s="83" t="n"/>
+      <c r="D18" s="88" t="n"/>
       <c r="E18" s="76" t="n"/>
       <c r="F18" s="77" t="n"/>
       <c r="G18" s="50" t="n"/>
@@ -1241,477 +1290,477 @@
       </c>
     </row>
     <row r="21" ht="22.05" customHeight="1" s="33">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="23" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="16">
+      <c r="B21" s="84" t="n"/>
+      <c r="C21" s="91" t="n"/>
+      <c r="D21" s="84" t="n"/>
+      <c r="E21" s="92" t="n"/>
+      <c r="F21" s="93">
         <f>IF(E21="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="94">
         <f>IF(E21="","",MIN(E21*F21,$D$16))</f>
         <v/>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="93">
         <f>IF(E21="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="94">
         <f>IF(E21="","",E21*H21)</f>
         <v/>
       </c>
-      <c r="J21" s="73" t="n"/>
-      <c r="K21" s="53">
+      <c r="J21" s="95" t="n"/>
+      <c r="K21" s="96">
         <f>IF(E21="","",E21-G21-I21-N(J21))</f>
         <v/>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="94">
         <f>IF(E21="","",$D$16-SUM(G$21:G21))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="22.05" customHeight="1" s="33">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="90" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="23" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="16">
+      <c r="B22" s="84" t="n"/>
+      <c r="C22" s="91" t="n"/>
+      <c r="D22" s="84" t="n"/>
+      <c r="E22" s="92" t="n"/>
+      <c r="F22" s="93">
         <f>IF(E22="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="94">
         <f>IF(E22="","",MIN(E22*F22,$D$16-SUM(G$20:G21)))</f>
         <v/>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="93">
         <f>IF(E22="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="94">
         <f>IF(E22="","",E22*H22)</f>
         <v/>
       </c>
-      <c r="J22" s="73" t="n"/>
-      <c r="K22" s="53">
+      <c r="J22" s="95" t="n"/>
+      <c r="K22" s="96">
         <f>IF(E22="","",E22-G22-I22-N(J22))</f>
         <v/>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="94">
         <f>IF(E22="","",$D$16-SUM(G$21:G22))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="22.05" customHeight="1" s="33">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="90" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="16">
+      <c r="B23" s="84" t="n"/>
+      <c r="C23" s="91" t="n"/>
+      <c r="D23" s="84" t="n"/>
+      <c r="E23" s="92" t="n"/>
+      <c r="F23" s="93">
         <f>IF(E23="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="94">
         <f>IF(E23="","",MIN(E23*F23,$D$16-SUM(G$20:G22)))</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="93">
         <f>IF(E23="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="94">
         <f>IF(E23="","",E23*H23)</f>
         <v/>
       </c>
-      <c r="J23" s="73" t="n"/>
-      <c r="K23" s="53">
+      <c r="J23" s="95" t="n"/>
+      <c r="K23" s="96">
         <f>IF(E23="","",E23-G23-I23-N(J23))</f>
         <v/>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="94">
         <f>IF(E23="","",$D$16-SUM(G$21:G23))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="22.05" customHeight="1" s="33">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="90" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="16">
+      <c r="B24" s="84" t="n"/>
+      <c r="C24" s="91" t="n"/>
+      <c r="D24" s="84" t="n"/>
+      <c r="E24" s="92" t="n"/>
+      <c r="F24" s="93">
         <f>IF(E24="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="94">
         <f>IF(E24="","",MIN(E24*F24,$D$16-SUM(G$20:G23)))</f>
         <v/>
       </c>
-      <c r="H24" s="72">
+      <c r="H24" s="97">
         <f>IF(E24="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="94">
         <f>IF(E24="","",E24*H24)</f>
         <v/>
       </c>
-      <c r="J24" s="73" t="n"/>
-      <c r="K24" s="53">
+      <c r="J24" s="95" t="n"/>
+      <c r="K24" s="96">
         <f>IF(E24="","",E24-G24-I24-N(J24))</f>
         <v/>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="94">
         <f>IF(E24="","",$D$16-SUM(G$21:G24))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="22.05" customHeight="1" s="33">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="90" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="16">
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="91" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="92" t="n"/>
+      <c r="F25" s="93">
         <f>IF(E25="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="94">
         <f>IF(E25="","",MIN(E25*F25,$D$16-SUM(G$20:G24)))</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="93">
         <f>IF(E25="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="94">
         <f>IF(E25="","",E25*H25)</f>
         <v/>
       </c>
-      <c r="J25" s="73" t="n"/>
-      <c r="K25" s="53">
+      <c r="J25" s="95" t="n"/>
+      <c r="K25" s="96">
         <f>IF(E25="","",E25-G25-I25-N(J25))</f>
         <v/>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="94">
         <f>IF(E25="","",$D$16-SUM(G$21:G25))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="22.05" customHeight="1" s="33">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="90" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="16">
+      <c r="B26" s="84" t="n"/>
+      <c r="C26" s="91" t="n"/>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="92" t="n"/>
+      <c r="F26" s="93">
         <f>IF(E26="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="94">
         <f>IF(E26="","",MIN(E26*F26,$D$16-SUM(G$20:G25)))</f>
         <v/>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="93">
         <f>IF(E26="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="94">
         <f>IF(E26="","",E26*H26)</f>
         <v/>
       </c>
-      <c r="J26" s="73" t="n"/>
-      <c r="K26" s="53">
+      <c r="J26" s="95" t="n"/>
+      <c r="K26" s="96">
         <f>IF(E26="","",E26-G26-I26-N(J26))</f>
         <v/>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="94">
         <f>IF(E26="","",$D$16-SUM(G$21:G26))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="22.05" customHeight="1" s="33">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="90" t="n">
         <v>7</v>
       </c>
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="16">
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="91" t="n"/>
+      <c r="D27" s="84" t="n"/>
+      <c r="E27" s="92" t="n"/>
+      <c r="F27" s="93">
         <f>IF(E27="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="94">
         <f>IF(E27="","",MIN(E27*F27,$D$16-SUM(G$20:G26)))</f>
         <v/>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="93">
         <f>IF(E27="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="94">
         <f>IF(E27="","",E27*H27)</f>
         <v/>
       </c>
-      <c r="J27" s="73" t="n"/>
-      <c r="K27" s="53">
+      <c r="J27" s="95" t="n"/>
+      <c r="K27" s="96">
         <f>IF(E27="","",E27-G27-I27-N(J27))</f>
         <v/>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="94">
         <f>IF(E27="","",$D$16-SUM(G$21:G27))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="22.05" customHeight="1" s="33">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="90" t="n">
         <v>8</v>
       </c>
-      <c r="B28" s="23" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="16">
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="91" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="92" t="n"/>
+      <c r="F28" s="93">
         <f>IF(E28="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="94">
         <f>IF(E28="","",MIN(E28*F28,$D$16-SUM(G$20:G27)))</f>
         <v/>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="93">
         <f>IF(E28="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="94">
         <f>IF(E28="","",E28*H28)</f>
         <v/>
       </c>
-      <c r="J28" s="73" t="n"/>
-      <c r="K28" s="53">
+      <c r="J28" s="95" t="n"/>
+      <c r="K28" s="96">
         <f>IF(E28="","",E28-G28-I28-N(J28))</f>
         <v/>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="94">
         <f>IF(E28="","",$D$16-SUM(G$21:G28))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="22.05" customHeight="1" s="33">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="90" t="n">
         <v>9</v>
       </c>
-      <c r="B29" s="23" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="16">
+      <c r="B29" s="84" t="n"/>
+      <c r="C29" s="91" t="n"/>
+      <c r="D29" s="84" t="n"/>
+      <c r="E29" s="92" t="n"/>
+      <c r="F29" s="93">
         <f>IF(E29="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="94">
         <f>IF(E29="","",MIN(E29*F29,$D$16-SUM(G$20:G28)))</f>
         <v/>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="93">
         <f>IF(E29="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="94">
         <f>IF(E29="","",E29*H29)</f>
         <v/>
       </c>
-      <c r="J29" s="73" t="n"/>
-      <c r="K29" s="53">
+      <c r="J29" s="95" t="n"/>
+      <c r="K29" s="96">
         <f>IF(E29="","",E29-G29-I29-N(J29))</f>
         <v/>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="94">
         <f>IF(E29="","",$D$16-SUM(G$21:G29))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="22.05" customHeight="1" s="33">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="90" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="23" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="16">
+      <c r="B30" s="84" t="n"/>
+      <c r="C30" s="91" t="n"/>
+      <c r="D30" s="84" t="n"/>
+      <c r="E30" s="92" t="n"/>
+      <c r="F30" s="93">
         <f>IF(E30="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="94">
         <f>IF(E30="","",MIN(E30*F30,$D$16-SUM(G$20:G29)))</f>
         <v/>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="93">
         <f>IF(E30="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="94">
         <f>IF(E30="","",E30*H30)</f>
         <v/>
       </c>
-      <c r="J30" s="73" t="n"/>
-      <c r="K30" s="53">
+      <c r="J30" s="95" t="n"/>
+      <c r="K30" s="96">
         <f>IF(E30="","",E30-G30-I30-N(J30))</f>
         <v/>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="94">
         <f>IF(E30="","",$D$16-SUM(G$21:G30))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="22.05" customHeight="1" s="33">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="90" t="n">
         <v>11</v>
       </c>
-      <c r="B31" s="23" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="16">
+      <c r="B31" s="84" t="n"/>
+      <c r="C31" s="91" t="n"/>
+      <c r="D31" s="84" t="n"/>
+      <c r="E31" s="92" t="n"/>
+      <c r="F31" s="93">
         <f>IF(E31="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="94">
         <f>IF(E31="","",MIN(E31*F31,$D$16-SUM(G$20:G30)))</f>
         <v/>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="93">
         <f>IF(E31="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="94">
         <f>IF(E31="","",E31*H31)</f>
         <v/>
       </c>
-      <c r="J31" s="73" t="n"/>
-      <c r="K31" s="53">
+      <c r="J31" s="95" t="n"/>
+      <c r="K31" s="96">
         <f>IF(E31="","",E31-G31-I31-N(J31))</f>
         <v/>
       </c>
-      <c r="L31" s="8">
+      <c r="L31" s="94">
         <f>IF(E31="","",$D$16-SUM(G$21:G31))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="22.05" customHeight="1" s="33">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="90" t="n">
         <v>12</v>
       </c>
-      <c r="B32" s="23" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="16">
+      <c r="B32" s="84" t="n"/>
+      <c r="C32" s="91" t="n"/>
+      <c r="D32" s="84" t="n"/>
+      <c r="E32" s="92" t="n"/>
+      <c r="F32" s="93">
         <f>IF(E32="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="94">
         <f>IF(E32="","",MIN(E32*F32,$D$16-SUM(G$20:G31)))</f>
         <v/>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="93">
         <f>IF(E32="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="94">
         <f>IF(E32="","",E32*H32)</f>
         <v/>
       </c>
-      <c r="J32" s="73" t="n"/>
-      <c r="K32" s="53">
+      <c r="J32" s="95" t="n"/>
+      <c r="K32" s="96">
         <f>IF(E32="","",E32-G32-I32-N(J32))</f>
         <v/>
       </c>
-      <c r="L32" s="8">
+      <c r="L32" s="94">
         <f>IF(E32="","",$D$16-SUM(G$21:G32))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="22.05" customHeight="1" s="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="90" t="n">
         <v>13</v>
       </c>
-      <c r="B33" s="23" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="16">
+      <c r="B33" s="84" t="n"/>
+      <c r="C33" s="91" t="n"/>
+      <c r="D33" s="84" t="n"/>
+      <c r="E33" s="92" t="n"/>
+      <c r="F33" s="93">
         <f>IF(E33="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="94">
         <f>IF(E33="","",MIN(E33*F33,$D$16-SUM(G$20:G32)))</f>
         <v/>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="93">
         <f>IF(E33="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="94">
         <f>IF(E33="","",E33*H33)</f>
         <v/>
       </c>
-      <c r="J33" s="73" t="n"/>
-      <c r="K33" s="53">
+      <c r="J33" s="95" t="n"/>
+      <c r="K33" s="96">
         <f>IF(E33="","",E33-G33-I33-N(J33))</f>
         <v/>
       </c>
-      <c r="L33" s="8">
+      <c r="L33" s="94">
         <f>IF(E33="","",$D$16-SUM(G$21:G33))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="22.05" customHeight="1" s="33">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="90" t="n">
         <v>14</v>
       </c>
-      <c r="B34" s="23" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="16">
+      <c r="B34" s="84" t="n"/>
+      <c r="C34" s="91" t="n"/>
+      <c r="D34" s="84" t="n"/>
+      <c r="E34" s="92" t="n"/>
+      <c r="F34" s="93">
         <f>IF(E34="","",$D$17)</f>
         <v/>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="94">
         <f>IF(E34="","",MIN(E34*F34,$D$16-SUM(G$20:G33)))</f>
         <v/>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="93">
         <f>IF(E34="","",$D$18)</f>
         <v/>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="94">
         <f>IF(E34="","",E34*H34)</f>
         <v/>
       </c>
-      <c r="J34" s="73" t="n"/>
-      <c r="K34" s="53">
+      <c r="J34" s="95" t="n"/>
+      <c r="K34" s="96">
         <f>IF(E34="","",E34-G34-I34-N(J34))</f>
         <v/>
       </c>
-      <c r="L34" s="8">
+      <c r="L34" s="94">
         <f>IF(E34="","",$D$16-SUM(G$21:G34))</f>
         <v/>
       </c>
@@ -1725,29 +1774,29 @@
       <c r="B35" s="76" t="n"/>
       <c r="C35" s="76" t="n"/>
       <c r="D35" s="77" t="n"/>
-      <c r="E35" s="9">
+      <c r="E35" s="98">
         <f>SUM(E21:E34)</f>
         <v/>
       </c>
       <c r="F35" s="34" t="n"/>
-      <c r="G35" s="9">
+      <c r="G35" s="98">
         <f>SUM(G21:G34)</f>
         <v/>
       </c>
       <c r="H35" s="34" t="n"/>
-      <c r="I35" s="9">
+      <c r="I35" s="98">
         <f>SUM(I21:I34)</f>
         <v/>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="98">
         <f>SUM(J21:J34)</f>
         <v/>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="98">
         <f>SUM(K21:K34)</f>
         <v/>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="98">
         <f>IF(D16="","",D16-G35)</f>
         <v/>
       </c>
@@ -1801,9 +1850,9 @@
       </c>
       <c r="B39" s="76" t="n"/>
       <c r="C39" s="77" t="n"/>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="76" t="n"/>
-      <c r="F39" s="77" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="85" t="n"/>
+      <c r="F39" s="86" t="n"/>
       <c r="G39" s="21" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -1811,9 +1860,9 @@
       </c>
       <c r="H39" s="76" t="n"/>
       <c r="I39" s="77" t="n"/>
-      <c r="J39" s="23" t="n"/>
-      <c r="K39" s="76" t="n"/>
-      <c r="L39" s="77" t="n"/>
+      <c r="J39" s="84" t="n"/>
+      <c r="K39" s="85" t="n"/>
+      <c r="L39" s="86" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="33">
       <c r="A40" s="21" t="inlineStr">
@@ -1823,9 +1872,9 @@
       </c>
       <c r="B40" s="76" t="n"/>
       <c r="C40" s="77" t="n"/>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="76" t="n"/>
-      <c r="F40" s="77" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="85" t="n"/>
+      <c r="F40" s="86" t="n"/>
       <c r="G40" s="21" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -1833,9 +1882,9 @@
       </c>
       <c r="H40" s="76" t="n"/>
       <c r="I40" s="77" t="n"/>
-      <c r="J40" s="23" t="n"/>
-      <c r="K40" s="76" t="n"/>
-      <c r="L40" s="77" t="n"/>
+      <c r="J40" s="84" t="n"/>
+      <c r="K40" s="85" t="n"/>
+      <c r="L40" s="86" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="33">
       <c r="A41" s="21" t="inlineStr">
@@ -1845,9 +1894,9 @@
       </c>
       <c r="B41" s="76" t="n"/>
       <c r="C41" s="77" t="n"/>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="76" t="n"/>
-      <c r="F41" s="77" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="85" t="n"/>
+      <c r="F41" s="86" t="n"/>
       <c r="G41" s="21" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -1855,11 +1904,12 @@
       </c>
       <c r="H41" s="76" t="n"/>
       <c r="I41" s="77" t="n"/>
-      <c r="J41" s="23" t="n"/>
-      <c r="K41" s="76" t="n"/>
-      <c r="L41" s="77" t="n"/>
+      <c r="J41" s="84" t="n"/>
+      <c r="K41" s="85" t="n"/>
+      <c r="L41" s="86" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="56">
     <mergeCell ref="D2:L2"/>
     <mergeCell ref="A41:C41"/>
